--- a/ARTICULO65/2026/FRACCION_XI/LGT_65_XI.xlsx
+++ b/ARTICULO65/2026/FRACCION_XI/LGT_65_XI.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bf5dc822e84b0775/Escritorio/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bf5dc822e84b0775/Escritorio/FRACCION_XI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_739DF4D017E89639F6592EDA6B5A9A46B90C4E4D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F09BCB53-816E-4D6A-9120-60B6908661C2}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_739DF4D017E89639F6592EDA6B5A9A46B90C4E4D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89E8CB47-A469-43EB-865D-6B6F5B5D17D4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,18 +18,14 @@
     <sheet name="Hidden_2" sheetId="3" r:id="rId3"/>
     <sheet name="Hidden_3" sheetId="4" r:id="rId4"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId5"/>
-    <externalReference r:id="rId6"/>
-  </externalReferences>
   <definedNames>
     <definedName name="Hidden_13">Hidden_1!$A$1:$A$11</definedName>
-    <definedName name="Hidden_14">[1]Hidden_1!$A$1:$A$11</definedName>
+    <definedName name="Hidden_14">#REF!</definedName>
     <definedName name="Hidden_211">Hidden_2!$A$1:$A$2</definedName>
-    <definedName name="Hidden_212">[2]Hidden_2!$A$1:$A$3</definedName>
-    <definedName name="Hidden_213">[1]Hidden_2!$A$1:$A$3</definedName>
+    <definedName name="Hidden_212">#REF!</definedName>
+    <definedName name="Hidden_213">#REF!</definedName>
     <definedName name="Hidden_312">Hidden_3!$A$1:$A$3</definedName>
-    <definedName name="Hidden_315">[1]Hidden_3!$A$1:$A$3</definedName>
+    <definedName name="Hidden_315">#REF!</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -41,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="107">
   <si>
     <t>15</t>
   </si>
@@ -254,9 +250,6 @@
   </si>
   <si>
     <t>Vicente</t>
-  </si>
-  <si>
-    <t>https://pdecolima.mx/</t>
   </si>
   <si>
     <t>Auxiliar Administrativo</t>
@@ -371,7 +364,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -389,14 +382,6 @@
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -441,9 +426,8 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -460,12 +444,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -479,152 +460,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Informacion"/>
-      <sheetName val="Hidden_1"/>
-      <sheetName val="Hidden_2"/>
-      <sheetName val="Hidden_3"/>
-      <sheetName val="Tabla_560607"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="A1" t="str">
-            <v>Funcionario [a]</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="A2" t="str">
-            <v>Servidor(a) público(a)</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>Servidor[a] público[a] eventual</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4" t="str">
-            <v>Integrante</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>Empleado [a]</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>Representante popular</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>Integrante del poder judicial</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8" t="str">
-            <v>Integrante de órgano autónomo</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9" t="str">
-            <v>Personal de confianza</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10" t="str">
-            <v>Prestador[a] de servicios profesionales</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11" t="str">
-            <v>Otro</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2">
-        <row r="1">
-          <cell r="A1" t="str">
-            <v>Hombre</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="A2" t="str">
-            <v>Mujer</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>No binario</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3">
-        <row r="1">
-          <cell r="A1" t="str">
-            <v>Inicio</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="A2" t="str">
-            <v>Modificación</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>Conclusión</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="4"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Reporte de Formatos"/>
-      <sheetName val="Hidden_1"/>
-      <sheetName val="Hidden_2"/>
-      <sheetName val="Hidden_3"/>
-      <sheetName val="Tabla_560607"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2">
-        <row r="1">
-          <cell r="A1" t="str">
-            <v>Hombre</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="A2" t="str">
-            <v>Mujer</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>No binario</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1171,11 +1006,11 @@
       <c r="M8" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="N8" s="4" t="s">
-        <v>71</v>
+      <c r="N8" s="8" t="s">
+        <v>106</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P8" s="3">
         <v>46203</v>
@@ -1198,25 +1033,25 @@
         <v>50</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>67</v>
       </c>
       <c r="I9" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="J9" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="K9" s="4" t="s">
         <v>74</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>75</v>
       </c>
       <c r="L9" s="4" t="s">
         <v>60</v>
@@ -1225,10 +1060,10 @@
         <v>63</v>
       </c>
       <c r="N9" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P9" s="3">
         <v>46203</v>
@@ -1252,25 +1087,25 @@
         <v>50</v>
       </c>
       <c r="E10" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>77</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>78</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>67</v>
       </c>
       <c r="I10" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="J10" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="K10" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>81</v>
       </c>
       <c r="L10" s="4" t="s">
         <v>61</v>
@@ -1279,10 +1114,10 @@
         <v>63</v>
       </c>
       <c r="N10" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P10" s="3">
         <v>46203</v>
@@ -1306,25 +1141,25 @@
         <v>50</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>67</v>
       </c>
       <c r="I11" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J11" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="K11" s="4" t="s">
         <v>83</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>84</v>
       </c>
       <c r="L11" s="4" t="s">
         <v>61</v>
@@ -1333,10 +1168,10 @@
         <v>63</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P11" s="3">
         <v>46203</v>
@@ -1360,25 +1195,25 @@
         <v>50</v>
       </c>
       <c r="E12" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="G12" s="4" t="s">
         <v>86</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>87</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>67</v>
       </c>
       <c r="I12" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J12" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="J12" s="4" t="s">
+      <c r="K12" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>90</v>
       </c>
       <c r="L12" s="4" t="s">
         <v>60</v>
@@ -1387,10 +1222,10 @@
         <v>63</v>
       </c>
       <c r="N12" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P12" s="3">
         <v>46203</v>
@@ -1414,25 +1249,25 @@
         <v>50</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>67</v>
       </c>
       <c r="I13" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="J13" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="K13" s="4" t="s">
         <v>92</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>93</v>
       </c>
       <c r="L13" s="4" t="s">
         <v>61</v>
@@ -1441,10 +1276,10 @@
         <v>63</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P13" s="3">
         <v>46203</v>
@@ -1468,25 +1303,25 @@
         <v>50</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>67</v>
       </c>
       <c r="I14" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="J14" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="K14" s="4" t="s">
         <v>95</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>96</v>
       </c>
       <c r="L14" s="4" t="s">
         <v>60</v>
@@ -1495,10 +1330,10 @@
         <v>63</v>
       </c>
       <c r="N14" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P14" s="3">
         <v>46203</v>
@@ -1522,25 +1357,25 @@
         <v>50</v>
       </c>
       <c r="E15" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="G15" s="4" t="s">
         <v>98</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>99</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>67</v>
       </c>
       <c r="I15" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="J15" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="J15" s="4" t="s">
+      <c r="K15" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>81</v>
       </c>
       <c r="L15" s="4" t="s">
         <v>61</v>
@@ -1549,10 +1384,10 @@
         <v>63</v>
       </c>
       <c r="N15" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O15" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P15" s="3">
         <v>46203</v>
@@ -1576,25 +1411,25 @@
         <v>50</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>67</v>
       </c>
       <c r="I16" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="J16" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="J16" s="4" t="s">
+      <c r="K16" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>102</v>
       </c>
       <c r="L16" s="4" t="s">
         <v>61</v>
@@ -1603,10 +1438,10 @@
         <v>63</v>
       </c>
       <c r="N16" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P16" s="3">
         <v>46203</v>
@@ -1630,25 +1465,25 @@
         <v>50</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>67</v>
       </c>
       <c r="I17" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="J17" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="J17" s="4" t="s">
+      <c r="K17" s="4" t="s">
         <v>104</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>105</v>
       </c>
       <c r="L17" s="4" t="s">
         <v>61</v>
@@ -1657,10 +1492,10 @@
         <v>63</v>
       </c>
       <c r="N17" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P17" s="3">
         <v>46203</v>
@@ -1700,10 +1535,6 @@
       <formula1>Hidden_315</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="N9" r:id="rId1" xr:uid="{3BF5AAB9-6817-4F88-A541-013EAEAAC382}"/>
-    <hyperlink ref="N10:N17" r:id="rId2" display="https://www.plataformadigitalnacional.org/declaraciones" xr:uid="{1ACCD2B3-95ED-4F95-BEB0-B61B353E2BDE}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
